--- a/_files/CA.xlsx
+++ b/_files/CA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zeluzjunior\PycharmProjects\teste_visual\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zeluzjunior\PycharmProjects\teste_visual\_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06AEE3A1-1DD9-4E5E-9131-11B1EEF5E42C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5126A14-2A43-43F0-A964-459F9431F5A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{80377A40-107F-4EA7-AA3F-2F03C9CD5D79}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="146">
   <si>
     <t>CA</t>
   </si>
@@ -459,6 +459,21 @@
   </si>
   <si>
     <t>local</t>
+  </si>
+  <si>
+    <t>imagem</t>
+  </si>
+  <si>
+    <t>APOIO</t>
+  </si>
+  <si>
+    <t>UTILIDADES</t>
+  </si>
+  <si>
+    <t>EXTERNA</t>
+  </si>
+  <si>
+    <t>INDEFINIDO</t>
   </si>
 </sst>
 </file>
@@ -494,8 +509,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -830,18 +848,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EA950AD-BB56-40DD-86D0-944FD7955EEB}">
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" style="1" customWidth="1"/>
     <col min="5" max="5" width="27.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -851,7 +869,7 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>139</v>
       </c>
       <c r="E1" t="s">
@@ -860,8 +878,11 @@
       <c r="F1" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>213</v>
       </c>
@@ -874,8 +895,11 @@
       <c r="E2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>453</v>
       </c>
@@ -888,8 +912,11 @@
       <c r="E3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>728</v>
       </c>
@@ -902,8 +929,11 @@
       <c r="E4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1155</v>
       </c>
@@ -916,8 +946,11 @@
       <c r="E5" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1163</v>
       </c>
@@ -930,8 +963,11 @@
       <c r="E6" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F6" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1171</v>
       </c>
@@ -944,8 +980,11 @@
       <c r="E7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F7" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1180</v>
       </c>
@@ -958,8 +997,11 @@
       <c r="E8" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F8" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1210</v>
       </c>
@@ -969,11 +1011,17 @@
       <c r="C9" t="s">
         <v>20</v>
       </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
       <c r="E9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F9" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1228</v>
       </c>
@@ -983,11 +1031,17 @@
       <c r="C10" t="s">
         <v>22</v>
       </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
       <c r="E10" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F10" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>1236</v>
       </c>
@@ -997,11 +1051,17 @@
       <c r="C11" t="s">
         <v>24</v>
       </c>
+      <c r="D11" s="1">
+        <v>2</v>
+      </c>
       <c r="E11" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F11" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>1244</v>
       </c>
@@ -1011,11 +1071,17 @@
       <c r="C12" t="s">
         <v>26</v>
       </c>
+      <c r="D12" s="1">
+        <v>2</v>
+      </c>
       <c r="E12" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F12" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>1295</v>
       </c>
@@ -1025,11 +1091,17 @@
       <c r="C13" t="s">
         <v>28</v>
       </c>
+      <c r="D13" s="1">
+        <v>3</v>
+      </c>
       <c r="E13" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F13" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>1538</v>
       </c>
@@ -1042,8 +1114,11 @@
       <c r="E14" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F14" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>1708</v>
       </c>
@@ -1056,8 +1131,11 @@
       <c r="E15" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F15" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>1724</v>
       </c>
@@ -1069,6 +1147,9 @@
       </c>
       <c r="E16" t="s">
         <v>6</v>
+      </c>
+      <c r="F16" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1084,6 +1165,9 @@
       <c r="E17" t="s">
         <v>6</v>
       </c>
+      <c r="F17" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
@@ -1098,6 +1182,9 @@
       <c r="E18" t="s">
         <v>6</v>
       </c>
+      <c r="F18" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
@@ -1112,6 +1199,9 @@
       <c r="E19" t="s">
         <v>6</v>
       </c>
+      <c r="F19" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
@@ -1126,6 +1216,9 @@
       <c r="E20" t="s">
         <v>6</v>
       </c>
+      <c r="F20" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
@@ -1140,6 +1233,9 @@
       <c r="E21" t="s">
         <v>6</v>
       </c>
+      <c r="F21" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
@@ -1154,6 +1250,9 @@
       <c r="E22" t="s">
         <v>6</v>
       </c>
+      <c r="F22" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
@@ -1168,6 +1267,9 @@
       <c r="E23" t="s">
         <v>6</v>
       </c>
+      <c r="F23" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
@@ -1182,6 +1284,9 @@
       <c r="E24" t="s">
         <v>6</v>
       </c>
+      <c r="F24" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
@@ -1196,6 +1301,9 @@
       <c r="E25" t="s">
         <v>6</v>
       </c>
+      <c r="F25" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
@@ -1210,6 +1318,9 @@
       <c r="E26" t="s">
         <v>6</v>
       </c>
+      <c r="F26" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
@@ -1224,6 +1335,9 @@
       <c r="E27" t="s">
         <v>6</v>
       </c>
+      <c r="F27" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
@@ -1238,6 +1352,9 @@
       <c r="E28" t="s">
         <v>6</v>
       </c>
+      <c r="F28" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
@@ -1252,6 +1369,9 @@
       <c r="E29" t="s">
         <v>6</v>
       </c>
+      <c r="F29" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
@@ -1263,7 +1383,7 @@
       <c r="C30" t="s">
         <v>62</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="1">
         <v>1</v>
       </c>
       <c r="E30" t="s">
@@ -1283,7 +1403,7 @@
       <c r="C31" t="s">
         <v>66</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="1">
         <v>2</v>
       </c>
       <c r="E31" t="s">
@@ -1303,7 +1423,7 @@
       <c r="C32" t="s">
         <v>68</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="1">
         <v>3</v>
       </c>
       <c r="E32" t="s">
@@ -1323,7 +1443,7 @@
       <c r="C33" t="s">
         <v>70</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="1">
         <v>4</v>
       </c>
       <c r="E33" t="s">
@@ -1343,7 +1463,7 @@
       <c r="C34" t="s">
         <v>72</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="1">
         <v>5</v>
       </c>
       <c r="E34" t="s">
@@ -1363,7 +1483,7 @@
       <c r="C35" t="s">
         <v>74</v>
       </c>
-      <c r="D35">
+      <c r="D35" s="1">
         <v>6</v>
       </c>
       <c r="E35" t="s">
@@ -1383,7 +1503,7 @@
       <c r="C36" t="s">
         <v>76</v>
       </c>
-      <c r="D36">
+      <c r="D36" s="1">
         <v>7</v>
       </c>
       <c r="E36" t="s">
@@ -1403,7 +1523,7 @@
       <c r="C37" t="s">
         <v>78</v>
       </c>
-      <c r="D37">
+      <c r="D37" s="1">
         <v>8</v>
       </c>
       <c r="E37" t="s">
@@ -1423,7 +1543,7 @@
       <c r="C38" t="s">
         <v>80</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="1">
         <v>9</v>
       </c>
       <c r="E38" t="s">
@@ -1443,7 +1563,7 @@
       <c r="C39" t="s">
         <v>82</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="1">
         <v>10</v>
       </c>
       <c r="E39" t="s">
@@ -1463,7 +1583,7 @@
       <c r="C40" t="s">
         <v>85</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="1">
         <v>11</v>
       </c>
       <c r="E40" t="s">
@@ -1483,8 +1603,14 @@
       <c r="C41" t="s">
         <v>88</v>
       </c>
+      <c r="D41" s="1">
+        <v>4</v>
+      </c>
       <c r="E41" t="s">
         <v>6</v>
+      </c>
+      <c r="F41" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -1497,8 +1623,14 @@
       <c r="C42" t="s">
         <v>90</v>
       </c>
+      <c r="D42" s="1">
+        <v>5</v>
+      </c>
       <c r="E42" t="s">
         <v>6</v>
+      </c>
+      <c r="F42" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -1511,8 +1643,14 @@
       <c r="C43" t="s">
         <v>92</v>
       </c>
+      <c r="D43" s="1">
+        <v>6</v>
+      </c>
       <c r="E43" t="s">
         <v>6</v>
+      </c>
+      <c r="F43" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -1525,7 +1663,7 @@
       <c r="C44" t="s">
         <v>94</v>
       </c>
-      <c r="D44">
+      <c r="D44" s="1">
         <v>12</v>
       </c>
       <c r="E44" t="s">
@@ -1545,7 +1683,7 @@
       <c r="C45" t="s">
         <v>95</v>
       </c>
-      <c r="D45">
+      <c r="D45" s="1">
         <v>12</v>
       </c>
       <c r="E45" t="s">
@@ -1565,7 +1703,7 @@
       <c r="C46" t="s">
         <v>97</v>
       </c>
-      <c r="D46">
+      <c r="D46" s="1">
         <v>13</v>
       </c>
       <c r="E46" t="s">
@@ -1585,7 +1723,7 @@
       <c r="C47" t="s">
         <v>98</v>
       </c>
-      <c r="D47">
+      <c r="D47" s="1">
         <v>14</v>
       </c>
       <c r="E47" t="s">
@@ -1605,7 +1743,7 @@
       <c r="C48" t="s">
         <v>100</v>
       </c>
-      <c r="D48">
+      <c r="D48" s="1">
         <v>15</v>
       </c>
       <c r="E48" t="s">
@@ -1625,7 +1763,7 @@
       <c r="C49" t="s">
         <v>102</v>
       </c>
-      <c r="D49">
+      <c r="D49" s="1">
         <v>16</v>
       </c>
       <c r="E49" t="s">
@@ -1645,7 +1783,7 @@
       <c r="C50" t="s">
         <v>104</v>
       </c>
-      <c r="D50">
+      <c r="D50" s="1">
         <v>1</v>
       </c>
       <c r="E50" t="s">
@@ -1665,7 +1803,7 @@
       <c r="C51" t="s">
         <v>107</v>
       </c>
-      <c r="D51">
+      <c r="D51" s="1">
         <v>2</v>
       </c>
       <c r="E51" t="s">
@@ -1685,7 +1823,7 @@
       <c r="C52" t="s">
         <v>109</v>
       </c>
-      <c r="D52">
+      <c r="D52" s="1">
         <v>3</v>
       </c>
       <c r="E52" t="s">
@@ -1708,6 +1846,9 @@
       <c r="E53" t="s">
         <v>6</v>
       </c>
+      <c r="F53" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54">
@@ -1722,6 +1863,9 @@
       <c r="E54" t="s">
         <v>114</v>
       </c>
+      <c r="F54" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55">
@@ -1733,7 +1877,7 @@
       <c r="C55" t="s">
         <v>117</v>
       </c>
-      <c r="D55">
+      <c r="D55" s="1">
         <v>4</v>
       </c>
       <c r="E55" t="s">
@@ -1753,7 +1897,7 @@
       <c r="C56" t="s">
         <v>119</v>
       </c>
-      <c r="D56">
+      <c r="D56" s="1">
         <v>5</v>
       </c>
       <c r="E56" t="s">
@@ -1773,7 +1917,7 @@
       <c r="C57" t="s">
         <v>121</v>
       </c>
-      <c r="D57">
+      <c r="D57" s="1">
         <v>6</v>
       </c>
       <c r="E57" t="s">
@@ -1793,7 +1937,7 @@
       <c r="C58" t="s">
         <v>123</v>
       </c>
-      <c r="D58">
+      <c r="D58" s="1">
         <v>7</v>
       </c>
       <c r="E58" t="s">
@@ -1813,7 +1957,7 @@
       <c r="C59" t="s">
         <v>125</v>
       </c>
-      <c r="D59">
+      <c r="D59" s="1">
         <v>7</v>
       </c>
       <c r="E59" t="s">
@@ -1833,6 +1977,9 @@
       <c r="C60" t="s">
         <v>126</v>
       </c>
+      <c r="F60" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61">
@@ -1844,7 +1991,7 @@
       <c r="C61" t="s">
         <v>128</v>
       </c>
-      <c r="D61">
+      <c r="D61" s="1">
         <v>8</v>
       </c>
       <c r="E61" t="s">
@@ -1864,7 +2011,7 @@
       <c r="C62" t="s">
         <v>130</v>
       </c>
-      <c r="D62">
+      <c r="D62" s="1">
         <v>8</v>
       </c>
       <c r="E62" t="s">
@@ -1884,7 +2031,7 @@
       <c r="C63" t="s">
         <v>132</v>
       </c>
-      <c r="D63">
+      <c r="D63" s="1">
         <v>9</v>
       </c>
       <c r="E63" t="s">
@@ -1904,7 +2051,7 @@
       <c r="C64" t="s">
         <v>133</v>
       </c>
-      <c r="D64">
+      <c r="D64" s="1">
         <v>9</v>
       </c>
       <c r="E64" t="s">
@@ -1927,6 +2074,9 @@
       <c r="E65" t="s">
         <v>114</v>
       </c>
+      <c r="F65" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66">
@@ -1938,7 +2088,7 @@
       <c r="C66" t="s">
         <v>136</v>
       </c>
-      <c r="D66">
+      <c r="D66" s="1">
         <v>9</v>
       </c>
       <c r="E66" t="s">
@@ -1958,7 +2108,7 @@
       <c r="C67" t="s">
         <v>138</v>
       </c>
-      <c r="D67">
+      <c r="D67" s="1">
         <v>10</v>
       </c>
       <c r="E67" t="s">
